--- a/education_surveys/020_language_roots_and_structures_survey--education_surveys.xlsx
+++ b/education_surveys/020_language_roots_and_structures_survey--education_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>language_family_tree</t>
+          <t>language_family_tree_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>language_family_tree</t>
+          <t>Language Family Tree 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>linguistic_characteristics</t>
+          <t>linguistic_characteristics_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>linguistic_characteristics</t>
+          <t>Linguistic Characteristics 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>language_roots</t>
+          <t>language_roots_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>language_roots</t>
+          <t>Language Roots 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>prophets</t>
+          <t>Language Roots And Structures Survey Prophets</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>prophets_additional_info</t>
+          <t>Language Roots And Structures Survey Prophets Additional Info</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>prophets</t>
+          <t>Language Roots And Structures Survey Prophets Prophet</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1364,7 +1364,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>language_family_tree_choices</t>
+          <t>language_family_tree_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1381,7 +1381,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>language_family_tree_choices</t>
+          <t>language_family_tree_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1398,7 +1398,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>linguistic_characteristics_choices</t>
+          <t>linguistic_characteristics_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>linguistic_characteristics_choices</t>
+          <t>linguistic_characteristics_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1432,7 +1432,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>language_roots_choices</t>
+          <t>language_roots_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1449,7 +1449,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>language_roots_choices</t>
+          <t>language_roots_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
